--- a/diseases/d125/2026-2029.xlsx
+++ b/diseases/d125/2026-2029.xlsx
@@ -11073,6 +11073,154 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>D125</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>vancomycin-resistance</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Vancomycin resistance</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>D125</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Vancomycin resistance</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>万古霉素耐药性</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP62" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR62" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS62" t="inlineStr"/>
+      <c r="AT62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV62" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA62" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB62" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC62" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11106,7 +11254,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -11189,7 +11337,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10">
@@ -11199,7 +11347,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d125/2026-2029.xlsx
+++ b/diseases/d125/2026-2029.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>31</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0.548382505996607</v>
       </c>
@@ -1161,9 +1158,6 @@
       <c r="O4" t="n">
         <v>66</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0.6167621082667007</v>
       </c>
@@ -2149,9 +2143,6 @@
       <c r="O10" t="n">
         <v>34</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0.6014517807704721</v>
       </c>
@@ -2545,9 +2536,6 @@
       <c r="O12" t="n">
         <v>65</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0.6074172278384175</v>
       </c>
@@ -3533,9 +3521,6 @@
       <c r="O18" t="n">
         <v>15</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0.2653463738693259</v>
       </c>
@@ -3929,9 +3914,6 @@
       <c r="O20" t="n">
         <v>107</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0.9999022058263181</v>
       </c>
@@ -4917,9 +4899,6 @@
       <c r="O26" t="n">
         <v>16</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0.283036132127281</v>
       </c>
@@ -5313,9 +5292,6 @@
       <c r="O28" t="n">
         <v>72</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0.6728313908364009</v>
       </c>
@@ -6301,9 +6277,6 @@
       <c r="O34" t="n">
         <v>26</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0.4599337147068316</v>
       </c>
@@ -6697,9 +6670,6 @@
       <c r="O36" t="n">
         <v>38</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0.3551054562747671</v>
       </c>
@@ -7833,9 +7803,6 @@
       <c r="O43" t="n">
         <v>21</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0.3714849234170563</v>
       </c>
@@ -8229,9 +8196,6 @@
       <c r="O45" t="n">
         <v>55</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0.513968423555584</v>
       </c>
@@ -8625,9 +8589,6 @@
       <c r="O47" t="n">
         <v>1</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0.0008168084075657662</v>
       </c>
@@ -8773,9 +8734,6 @@
       <c r="O48" t="n">
         <v>2</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0.001633616815131532</v>
       </c>
@@ -8921,9 +8879,6 @@
       <c r="O49" t="n">
         <v>0</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
@@ -9069,9 +9024,6 @@
       <c r="O50" t="n">
         <v>1</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0.0008168084075657662</v>
       </c>
@@ -9212,16 +9164,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O51" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="R51" t="n">
-        <v>0.3537951651591013</v>
+        <v>0.3714849234170563</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -9374,10 +9323,10 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O52" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="U52" t="inlineStr">
         <is>
@@ -9613,9 +9562,6 @@
       <c r="O53" t="n">
         <v>52</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0.485933782270734</v>
       </c>
@@ -10009,9 +9955,6 @@
       <c r="O55" t="n">
         <v>0</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
@@ -10157,9 +10100,6 @@
       <c r="O56" t="n">
         <v>0</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
@@ -10305,9 +10245,6 @@
       <c r="O57" t="n">
         <v>1</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0.0008168084075657662</v>
       </c>
@@ -10453,9 +10390,6 @@
       <c r="O58" t="n">
         <v>0</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
@@ -10601,9 +10535,6 @@
       <c r="O59" t="n">
         <v>3</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0.002450425222697299</v>
       </c>
@@ -10744,16 +10675,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O60" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R60" t="n">
-        <v>0.01768975825795506</v>
+        <v>0.08844879128977531</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -10906,10 +10834,10 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O61" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U61" t="inlineStr">
         <is>
@@ -11143,9 +11071,6 @@
         <v>0</v>
       </c>
       <c r="O62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q62" t="n">
         <v>0</v>
       </c>
       <c r="R62" t="n">
@@ -11399,7 +11324,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>655</v>
+        <v>660</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d125/2026-2029.xlsx
+++ b/diseases/d125/2026-2029.xlsx
@@ -11146,6 +11146,151 @@
         </is>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>D125</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>vancomycin-resistance</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Vancomycin resistance</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>D125</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Vancomycin resistance</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>万古霉素耐药性</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP63" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR63" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS63" t="inlineStr"/>
+      <c r="AT63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV63" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA63" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB63" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC63" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11179,7 +11324,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -11262,7 +11407,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10">
@@ -11272,7 +11417,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d125/2026-2029.xlsx
+++ b/diseases/d125/2026-2029.xlsx
@@ -10675,13 +10675,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O60" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R60" t="n">
-        <v>0.08844879128977531</v>
+        <v>0.1238283078056854</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -10834,10 +10834,10 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O61" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U61" t="inlineStr">
         <is>
@@ -11469,7 +11469,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d125/2026-2029.xlsx
+++ b/diseases/d125/2026-2029.xlsx
@@ -9164,13 +9164,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O51" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R51" t="n">
-        <v>0.3714849234170563</v>
+        <v>0.3891746816750113</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -9323,10 +9323,10 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O52" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U52" t="inlineStr">
         <is>
@@ -10675,13 +10675,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="O60" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="R60" t="n">
-        <v>0.1238283078056854</v>
+        <v>0.2476566156113709</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -10834,10 +10834,10 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="O61" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="U61" t="inlineStr">
         <is>
@@ -11286,6 +11286,151 @@
         </is>
       </c>
       <c r="BC63" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>D125</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>vancomycin-resistance</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Vancomycin resistance</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>D125</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Vancomycin resistance</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>万古霉素耐药性</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N64" t="n">
+        <v>1</v>
+      </c>
+      <c r="O64" t="n">
+        <v>1</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP64" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR64" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS64" t="inlineStr"/>
+      <c r="AT64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV64" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA64" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB64" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC64" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -11324,7 +11469,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -11407,7 +11552,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10">
@@ -11417,7 +11562,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11">
@@ -11469,7 +11614,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>662</v>
+        <v>671</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d125/2026-2029.xlsx
+++ b/diseases/d125/2026-2029.xlsx
@@ -9164,13 +9164,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O51" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="R51" t="n">
-        <v>0.3891746816750113</v>
+        <v>0.4245541981909216</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -9323,10 +9323,10 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O52" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="U52" t="inlineStr">
         <is>
@@ -10675,13 +10675,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O60" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="R60" t="n">
-        <v>0.2476566156113709</v>
+        <v>0.283036132127281</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -10834,10 +10834,10 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O61" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="U61" t="inlineStr">
         <is>
@@ -11433,6 +11433,544 @@
       <c r="BC64" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>D125</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>vancomycin-resistance</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Vancomycin resistance</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>D125</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Vancomycin resistance</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>万古霉素耐药性</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N65" t="n">
+        <v>1</v>
+      </c>
+      <c r="O65" t="n">
+        <v>1</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP65" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR65" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS65" t="inlineStr"/>
+      <c r="AT65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV65" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA65" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB65" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC65" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>D125</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>vancomycin-resistance</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Vancomycin resistance</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>D125</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Vancomycin resistance</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>万古霉素耐药性</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N66" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_803_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP66" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ66" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS66" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_803_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV66" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA66" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB66" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC66" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>D125</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>vancomycin-resistance</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Vancomycin resistance</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>D125</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Vancomycin resistance</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>万古霉素耐药性</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N67" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0</v>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_803_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_803_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>Resistent enterokokk</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD67" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE67" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF67" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG67" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS resistant-enterococcus category.</t>
+        </is>
+      </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN67" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP67" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ67" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS67" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_803_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV67" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA67" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB67" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC67" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -11469,7 +12007,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -11552,7 +12090,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10">
@@ -11562,7 +12100,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11">
@@ -11582,7 +12120,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
@@ -11614,7 +12152,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>671</v>
+        <v>676</v>
       </c>
     </row>
     <row r="16">
